--- a/data/MK_INV_DATA_20260608.xlsx
+++ b/data/MK_INV_DATA_20260608.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1547.38</v>
+        <v>1548.88</v>
       </c>
       <c r="F7" t="n">
         <v>1558.84</v>
@@ -687,11 +687,11 @@
         <v>1559.44</v>
       </c>
       <c r="H7" t="n">
-        <v>1547.38</v>
+        <v>1545.78</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="8">
@@ -710,11 +710,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260607</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230.57</v>
+        <v>228.45</v>
       </c>
       <c r="F8" t="n">
         <v>230.48</v>
@@ -723,7 +723,7 @@
         <v>230.57</v>
       </c>
       <c r="H8" t="n">
-        <v>230.48</v>
+        <v>228.35</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.647</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>9.706</v>
@@ -935,11 +935,11 @@
         <v>9.711</v>
       </c>
       <c r="H14" t="n">
-        <v>9.647</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.007</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="15">
@@ -1318,20 +1318,20 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92.56</v>
+        <v>93.31</v>
       </c>
       <c r="F25" t="n">
         <v>93</v>
       </c>
       <c r="G25" t="n">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="H25" t="n">
-        <v>92.36</v>
+        <v>92.2</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.0223</v>
+        <v>0.0306</v>
       </c>
     </row>
     <row r="26">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4369</v>
+        <v>4347.8</v>
       </c>
       <c r="F31" t="n">
         <v>4354</v>
@@ -1561,15 +1561,15 @@
         <v>4377.5</v>
       </c>
       <c r="H31" t="n">
-        <v>4333.4</v>
+        <v>4323.6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.02K</t>
+          <t>19.22K</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.0074</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="32">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7477.46</v>
+        <v>7591.56</v>
       </c>
       <c r="F36" t="n">
         <v>8048.09</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.87K</t>
+          <t>171.70K</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-0.0837</v>
+        <v>-0.0697</v>
       </c>
     </row>
     <row r="37">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1186.44</v>
+        <v>1205.99</v>
       </c>
       <c r="F41" t="n">
         <v>1282.81</v>
@@ -1961,11 +1961,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.37K</t>
+          <t>72.38K</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.0853</v>
+        <v>-0.0702</v>
       </c>
     </row>
     <row r="42">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>935.77</v>
+        <v>928.6799999999999</v>
       </c>
       <c r="F46" t="n">
         <v>959.61</v>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>141.58K</t>
+          <t>299.69K</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>-0.0665</v>
+        <v>-0.0736</v>
       </c>
     </row>
     <row r="47">
